--- a/files/resources/modelli/comuni/adotta-il-modello-di-sito-comunale/definisci-architettura-e-contenuti/Architettura-informazione-sito-Comuni.xlsx
+++ b/files/resources/modelli/comuni/adotta-il-modello-di-sito-comunale/definisci-architettura-e-contenuti/Architettura-informazione-sito-Comuni.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielenole/Desktop/new modelli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielenole/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98B669C-16A2-7643-B0CF-1BB9CFD6EC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835B39D7-A3BA-0241-B931-BB280967E74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16380" firstSheet="31" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" firstSheet="18" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduzione" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="1173">
   <si>
     <t>v2.0</t>
   </si>
@@ -2288,9 +2288,6 @@
   </si>
   <si>
     <t>http://eurovoc.europa.eu/3967</t>
-  </si>
-  <si>
-    <t>Assistenza agli invalidi</t>
   </si>
   <si>
     <t>http://eurovoc.europa.eu/4209</t>
@@ -4477,9 +4474,6 @@
     <t>1…n</t>
   </si>
   <si>
-    <t>Persona con disabilità</t>
-  </si>
-  <si>
     <t>Testo breve (max. 70 char)</t>
   </si>
   <si>
@@ -4517,6 +4511,9 @@
   </si>
   <si>
     <t>Aggiunta della voce "Persona con disabilità alla tassonomia ARGOMENTI; aggiornamento della cardinalità dell'attributo Incarico per PERSONA PUBBLICA; Aggiornamento della cardinalità dell'attributo Persona per INCARICO; Aggiornamento del limite massimo dei titoli a 70 caratteri e delle descrizioni brevi a 160 caratteri per tutte le tipologie di contenuto.</t>
+  </si>
+  <si>
+    <t>Assistenza alle persone con disabilità</t>
   </si>
 </sst>
 </file>
@@ -5802,6 +5799,9 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="57" fillId="23" borderId="16" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5854,9 +5854,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="23" borderId="16" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6396,27 +6393,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="A1" s="180" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
       <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" s="149" customFormat="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="178" t="s">
         <v>363</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
       <c r="A3" s="150" t="s">
@@ -6453,7 +6450,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -6487,13 +6484,13 @@
         <v>234</v>
       </c>
       <c r="B6" s="127" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C6" s="100" t="s">
         <v>219</v>
       </c>
       <c r="D6" s="108" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E6" s="100"/>
       <c r="F6" s="100"/>
@@ -6810,27 +6807,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="180" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="117"/>
+    </row>
+    <row r="2" spans="1:8" s="104" customFormat="1">
+      <c r="A2" s="178" t="s">
         <v>1146</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="117"/>
-    </row>
-    <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="177" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -6868,7 +6865,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -6906,7 +6903,7 @@
         <v>228</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E6" s="99"/>
       <c r="F6" s="99"/>
@@ -6950,13 +6947,13 @@
         <v>331</v>
       </c>
       <c r="B9" s="108" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C9" s="100" t="s">
         <v>219</v>
       </c>
       <c r="D9" s="108" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E9" s="100"/>
       <c r="F9" s="100"/>
@@ -7346,27 +7343,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="180" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
+      <c r="A1" s="181" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
       <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="178" t="s">
         <v>413</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -7420,13 +7417,13 @@
         <v>416</v>
       </c>
       <c r="B5" s="158" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C5" s="100" t="s">
         <v>219</v>
       </c>
       <c r="D5" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E5" s="100"/>
       <c r="F5" s="100"/>
@@ -7480,7 +7477,7 @@
         <v>228</v>
       </c>
       <c r="D8" s="113" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E8" s="99"/>
       <c r="F8" s="99"/>
@@ -7512,13 +7509,13 @@
         <v>331</v>
       </c>
       <c r="B10" s="158" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C10" s="100" t="s">
         <v>219</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E10" s="100"/>
       <c r="F10" s="100"/>
@@ -8298,27 +8295,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="180" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="117"/>
+    </row>
+    <row r="2" spans="1:8" s="104" customFormat="1">
+      <c r="A2" s="178" t="s">
         <v>1149</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="117"/>
-    </row>
-    <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="177" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -8350,13 +8347,13 @@
         <v>463</v>
       </c>
       <c r="B4" s="108" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C4" s="100" t="s">
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -8512,7 +8509,7 @@
         <v>219</v>
       </c>
       <c r="D12" s="108" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E12" s="100"/>
       <c r="F12" s="100"/>
@@ -8886,27 +8883,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="180" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="117"/>
+    </row>
+    <row r="2" spans="1:8" s="104" customFormat="1">
+      <c r="A2" s="178" t="s">
         <v>1151</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="117"/>
-    </row>
-    <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="177" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -8944,7 +8941,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -8962,7 +8959,7 @@
         <v>219</v>
       </c>
       <c r="D5" s="108" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E5" s="98"/>
       <c r="F5" s="100"/>
@@ -9156,27 +9153,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="A1" s="180" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
       <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="182" t="s">
         <v>514</v>
       </c>
-      <c r="B2" s="181"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -9214,7 +9211,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -9436,27 +9433,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="A1" s="180" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
       <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="178" t="s">
         <v>530</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -9494,7 +9491,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="100" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -9737,27 +9734,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="180" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="117"/>
+    </row>
+    <row r="2" spans="1:8" s="104" customFormat="1">
+      <c r="A2" s="178" t="s">
         <v>1155</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="117"/>
-    </row>
-    <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="177" t="s">
-        <v>1156</v>
-      </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -9789,13 +9786,13 @@
         <v>463</v>
       </c>
       <c r="B4" s="108" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C4" s="100" t="s">
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -9933,7 +9930,7 @@
         <v>219</v>
       </c>
       <c r="D11" s="108" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E11" s="100"/>
       <c r="F11" s="100"/>
@@ -10225,27 +10222,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="A1" s="180" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
       <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="182" t="s">
+      <c r="A2" s="183" t="s">
         <v>556</v>
       </c>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
+      <c r="B2" s="183"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -10277,13 +10274,13 @@
         <v>557</v>
       </c>
       <c r="B4" s="108" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C4" s="100" t="s">
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -10477,27 +10474,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="36">
-      <c r="A1" s="179" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
+      <c r="A1" s="180" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
       <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="184" t="s">
         <v>570</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -10535,7 +10532,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="158"/>
       <c r="F4" s="100"/>
@@ -13319,7 +13316,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:Z267"/>
+  <dimension ref="A1:Z266"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="56.7109375" customWidth="1"/>
@@ -13329,16 +13326,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
         <v>583</v>
       </c>
-      <c r="B1" s="184"/>
+      <c r="B1" s="185"/>
     </row>
     <row r="2" spans="1:2" ht="22">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="186" t="s">
         <v>584</v>
       </c>
-      <c r="B2" s="185"/>
+      <c r="B2" s="186"/>
     </row>
     <row r="3" spans="1:2" ht="23">
       <c r="A3" s="60" t="s">
@@ -13390,495 +13387,493 @@
     </row>
     <row r="9" spans="1:2" ht="23">
       <c r="A9" s="61" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B9" s="62" t="s">
         <v>597</v>
-      </c>
-      <c r="B9" s="62" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="23">
       <c r="A10" s="61" t="s">
+        <v>598</v>
+      </c>
+      <c r="B10" s="62" t="s">
         <v>599</v>
-      </c>
-      <c r="B10" s="62" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="23">
       <c r="A11" s="61" t="s">
+        <v>600</v>
+      </c>
+      <c r="B11" s="62" t="s">
         <v>601</v>
-      </c>
-      <c r="B11" s="62" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="23">
       <c r="A12" s="61" t="s">
+        <v>602</v>
+      </c>
+      <c r="B12" s="62" t="s">
         <v>603</v>
-      </c>
-      <c r="B12" s="62" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="23">
       <c r="A13" s="61" t="s">
+        <v>604</v>
+      </c>
+      <c r="B13" s="62" t="s">
         <v>605</v>
-      </c>
-      <c r="B13" s="62" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="23">
       <c r="A14" s="61" t="s">
+        <v>606</v>
+      </c>
+      <c r="B14" s="62" t="s">
         <v>607</v>
-      </c>
-      <c r="B14" s="62" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="23">
       <c r="A15" s="61" t="s">
+        <v>608</v>
+      </c>
+      <c r="B15" s="62" t="s">
         <v>609</v>
-      </c>
-      <c r="B15" s="62" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="23">
       <c r="A16" s="61" t="s">
+        <v>610</v>
+      </c>
+      <c r="B16" s="62" t="s">
         <v>611</v>
-      </c>
-      <c r="B16" s="62" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="23">
       <c r="A17" s="61" t="s">
+        <v>612</v>
+      </c>
+      <c r="B17" s="62" t="s">
         <v>613</v>
-      </c>
-      <c r="B17" s="62" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="23">
       <c r="A18" s="61" t="s">
+        <v>614</v>
+      </c>
+      <c r="B18" s="62" t="s">
         <v>615</v>
-      </c>
-      <c r="B18" s="62" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="23">
       <c r="A19" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="B19" s="63" t="s">
         <v>617</v>
-      </c>
-      <c r="B19" s="63" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="23">
       <c r="A20" s="61" t="s">
+        <v>618</v>
+      </c>
+      <c r="B20" s="62" t="s">
         <v>619</v>
-      </c>
-      <c r="B20" s="62" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="23">
       <c r="A21" s="61" t="s">
+        <v>620</v>
+      </c>
+      <c r="B21" s="62" t="s">
         <v>621</v>
-      </c>
-      <c r="B21" s="62" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="23">
       <c r="A22" s="61" t="s">
+        <v>622</v>
+      </c>
+      <c r="B22" s="62" t="s">
         <v>623</v>
-      </c>
-      <c r="B22" s="62" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="23">
       <c r="A23" s="61" t="s">
+        <v>624</v>
+      </c>
+      <c r="B23" s="62" t="s">
         <v>625</v>
-      </c>
-      <c r="B23" s="62" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="23">
       <c r="A24" s="61" t="s">
+        <v>626</v>
+      </c>
+      <c r="B24" s="62" t="s">
         <v>627</v>
-      </c>
-      <c r="B24" s="62" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="23">
       <c r="A25" s="61" t="s">
+        <v>628</v>
+      </c>
+      <c r="B25" s="62" t="s">
         <v>629</v>
-      </c>
-      <c r="B25" s="62" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="23">
       <c r="A26" s="61" t="s">
+        <v>630</v>
+      </c>
+      <c r="B26" s="62" t="s">
         <v>631</v>
-      </c>
-      <c r="B26" s="62" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="23">
       <c r="A27" s="61" t="s">
+        <v>632</v>
+      </c>
+      <c r="B27" s="62" t="s">
         <v>633</v>
-      </c>
-      <c r="B27" s="62" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="23">
       <c r="A28" s="61" t="s">
+        <v>634</v>
+      </c>
+      <c r="B28" s="62" t="s">
         <v>635</v>
-      </c>
-      <c r="B28" s="62" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="23">
       <c r="A29" s="61" t="s">
+        <v>636</v>
+      </c>
+      <c r="B29" s="62" t="s">
         <v>637</v>
-      </c>
-      <c r="B29" s="62" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="23">
       <c r="A30" s="61" t="s">
+        <v>638</v>
+      </c>
+      <c r="B30" s="62" t="s">
         <v>639</v>
-      </c>
-      <c r="B30" s="62" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="23">
       <c r="A31" s="61" t="s">
+        <v>640</v>
+      </c>
+      <c r="B31" s="62" t="s">
         <v>641</v>
-      </c>
-      <c r="B31" s="62" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="23">
       <c r="A32" s="61" t="s">
+        <v>642</v>
+      </c>
+      <c r="B32" s="62" t="s">
         <v>643</v>
-      </c>
-      <c r="B32" s="62" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="23">
       <c r="A33" s="61" t="s">
+        <v>644</v>
+      </c>
+      <c r="B33" s="62" t="s">
         <v>645</v>
-      </c>
-      <c r="B33" s="62" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="23">
       <c r="A34" s="61" t="s">
+        <v>646</v>
+      </c>
+      <c r="B34" s="62" t="s">
         <v>647</v>
-      </c>
-      <c r="B34" s="62" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="23">
       <c r="A35" s="61" t="s">
+        <v>648</v>
+      </c>
+      <c r="B35" s="62" t="s">
         <v>649</v>
-      </c>
-      <c r="B35" s="62" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="23">
       <c r="A36" s="61" t="s">
+        <v>650</v>
+      </c>
+      <c r="B36" s="62" t="s">
         <v>651</v>
-      </c>
-      <c r="B36" s="62" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="23">
       <c r="A37" s="61" t="s">
+        <v>652</v>
+      </c>
+      <c r="B37" s="62" t="s">
         <v>653</v>
-      </c>
-      <c r="B37" s="62" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="23">
       <c r="A38" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="B38" s="62" t="s">
         <v>655</v>
-      </c>
-      <c r="B38" s="62" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="23">
       <c r="A39" s="61" t="s">
+        <v>656</v>
+      </c>
+      <c r="B39" s="62" t="s">
         <v>657</v>
-      </c>
-      <c r="B39" s="62" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="23">
       <c r="A40" s="61" t="s">
+        <v>658</v>
+      </c>
+      <c r="B40" s="62" t="s">
         <v>659</v>
-      </c>
-      <c r="B40" s="62" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="23">
       <c r="A41" s="61" t="s">
+        <v>660</v>
+      </c>
+      <c r="B41" s="62" t="s">
         <v>661</v>
-      </c>
-      <c r="B41" s="62" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="23">
       <c r="A42" s="61" t="s">
+        <v>662</v>
+      </c>
+      <c r="B42" s="62" t="s">
         <v>663</v>
-      </c>
-      <c r="B42" s="62" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="23">
       <c r="A43" s="61" t="s">
+        <v>664</v>
+      </c>
+      <c r="B43" s="62" t="s">
         <v>665</v>
-      </c>
-      <c r="B43" s="62" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="23">
       <c r="A44" s="61" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B44" s="62"/>
+        <v>666</v>
+      </c>
+      <c r="B44" s="62" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="45" spans="1:2" ht="23">
       <c r="A45" s="61" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B45" s="62" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="23">
       <c r="A46" s="61" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B46" s="62" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="23">
       <c r="A47" s="61" t="s">
-        <v>671</v>
-      </c>
-      <c r="B47" s="62" t="s">
         <v>672</v>
       </c>
+      <c r="B47" s="62"/>
     </row>
     <row r="48" spans="1:2" ht="23">
       <c r="A48" s="61" t="s">
         <v>673</v>
       </c>
-      <c r="B48" s="62"/>
+      <c r="B48" s="62" t="s">
+        <v>674</v>
+      </c>
     </row>
     <row r="49" spans="1:26" ht="23">
       <c r="A49" s="61" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B49" s="62" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="50" spans="1:26" ht="23">
       <c r="A50" s="61" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B50" s="62" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="51" spans="1:26" ht="23">
       <c r="A51" s="61" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B51" s="62" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52" spans="1:26" ht="23">
       <c r="A52" s="61" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B52" s="62" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="53" spans="1:26" ht="23">
       <c r="A53" s="61" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B53" s="62" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="54" spans="1:26" ht="23">
       <c r="A54" s="61" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B54" s="62" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="55" spans="1:26" ht="23">
       <c r="A55" s="61" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B55" s="62" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="56" spans="1:26" ht="23">
       <c r="A56" s="61" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B56" s="62" t="s">
-        <v>689</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
+      <c r="N56" s="30"/>
+      <c r="O56" s="30"/>
+      <c r="P56" s="30"/>
+      <c r="Q56" s="30"/>
+      <c r="R56" s="30"/>
+      <c r="S56" s="30"/>
+      <c r="T56" s="30"/>
+      <c r="U56" s="30"/>
+      <c r="V56" s="30"/>
+      <c r="W56" s="30"/>
+      <c r="X56" s="30"/>
+      <c r="Y56" s="30"/>
+      <c r="Z56" s="30"/>
     </row>
     <row r="57" spans="1:26" ht="23">
       <c r="A57" s="61" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B57" s="62" t="s">
-        <v>691</v>
-      </c>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="30"/>
-      <c r="K57" s="30"/>
-      <c r="L57" s="30"/>
-      <c r="M57" s="30"/>
-      <c r="N57" s="30"/>
-      <c r="O57" s="30"/>
-      <c r="P57" s="30"/>
-      <c r="Q57" s="30"/>
-      <c r="R57" s="30"/>
-      <c r="S57" s="30"/>
-      <c r="T57" s="30"/>
-      <c r="U57" s="30"/>
-      <c r="V57" s="30"/>
-      <c r="W57" s="30"/>
-      <c r="X57" s="30"/>
-      <c r="Y57" s="30"/>
-      <c r="Z57" s="30"/>
+        <v>692</v>
+      </c>
     </row>
     <row r="58" spans="1:26" ht="23">
       <c r="A58" s="61" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B58" s="62" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="59" spans="1:26" ht="23">
       <c r="A59" s="61" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B59" s="62" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="60" spans="1:26" ht="23">
       <c r="A60" s="61" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B60" s="62" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="61" spans="1:26" ht="23">
       <c r="A61" s="61" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B61" s="62" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="62" spans="1:26" ht="23">
       <c r="A62" s="61" t="s">
-        <v>700</v>
-      </c>
-      <c r="B62" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="63" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="63" spans="1:26" ht="23">
       <c r="A63" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="B63" s="63" t="s">
         <v>702</v>
+      </c>
+      <c r="B63" s="62" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="64" spans="1:26" ht="23">
       <c r="A64" s="61" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B64" s="62" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="23">
       <c r="A65" s="61" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B65" s="62" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="23">
       <c r="A66" s="61" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B66" s="62" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="23">
-      <c r="A67" s="61" t="s">
         <v>709</v>
       </c>
-      <c r="B67" s="62" t="s">
-        <v>710</v>
-      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="30"/>
@@ -14675,10 +14670,6 @@
     <row r="266" spans="1:2">
       <c r="A266" s="30"/>
       <c r="B266" s="30"/>
-    </row>
-    <row r="267" spans="1:2">
-      <c r="A267" s="30"/>
-      <c r="B267" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14727,28 +14718,28 @@
     <hyperlink ref="B41" r:id="rId39" xr:uid="{00000000-0004-0000-1300-000026000000}"/>
     <hyperlink ref="B42" r:id="rId40" xr:uid="{00000000-0004-0000-1300-000027000000}"/>
     <hyperlink ref="B43" r:id="rId41" xr:uid="{00000000-0004-0000-1300-000028000000}"/>
-    <hyperlink ref="B45" r:id="rId42" xr:uid="{00000000-0004-0000-1300-000029000000}"/>
-    <hyperlink ref="B46" r:id="rId43" xr:uid="{00000000-0004-0000-1300-00002A000000}"/>
-    <hyperlink ref="B47" r:id="rId44" xr:uid="{00000000-0004-0000-1300-00002B000000}"/>
-    <hyperlink ref="B49" r:id="rId45" xr:uid="{00000000-0004-0000-1300-00002C000000}"/>
-    <hyperlink ref="B50" r:id="rId46" xr:uid="{00000000-0004-0000-1300-00002D000000}"/>
-    <hyperlink ref="B51" r:id="rId47" xr:uid="{00000000-0004-0000-1300-00002E000000}"/>
-    <hyperlink ref="B52" r:id="rId48" xr:uid="{00000000-0004-0000-1300-00002F000000}"/>
-    <hyperlink ref="B53" r:id="rId49" xr:uid="{00000000-0004-0000-1300-000030000000}"/>
-    <hyperlink ref="B54" r:id="rId50" xr:uid="{00000000-0004-0000-1300-000031000000}"/>
-    <hyperlink ref="B55" r:id="rId51" xr:uid="{00000000-0004-0000-1300-000032000000}"/>
-    <hyperlink ref="B56" r:id="rId52" xr:uid="{00000000-0004-0000-1300-000033000000}"/>
-    <hyperlink ref="B57" r:id="rId53" xr:uid="{00000000-0004-0000-1300-000034000000}"/>
-    <hyperlink ref="B58" r:id="rId54" xr:uid="{00000000-0004-0000-1300-000035000000}"/>
-    <hyperlink ref="B59" r:id="rId55" xr:uid="{00000000-0004-0000-1300-000036000000}"/>
-    <hyperlink ref="B60" r:id="rId56" xr:uid="{00000000-0004-0000-1300-000037000000}"/>
-    <hyperlink ref="B61" r:id="rId57" xr:uid="{00000000-0004-0000-1300-000038000000}"/>
-    <hyperlink ref="B62" r:id="rId58" xr:uid="{00000000-0004-0000-1300-000039000000}"/>
-    <hyperlink ref="B63" r:id="rId59" xr:uid="{00000000-0004-0000-1300-00003A000000}"/>
-    <hyperlink ref="B64" r:id="rId60" xr:uid="{00000000-0004-0000-1300-00003B000000}"/>
-    <hyperlink ref="B65" r:id="rId61" xr:uid="{00000000-0004-0000-1300-00003C000000}"/>
-    <hyperlink ref="B66" r:id="rId62" xr:uid="{00000000-0004-0000-1300-00003D000000}"/>
-    <hyperlink ref="B67" r:id="rId63" xr:uid="{00000000-0004-0000-1300-00003E000000}"/>
+    <hyperlink ref="B44" r:id="rId42" xr:uid="{00000000-0004-0000-1300-000029000000}"/>
+    <hyperlink ref="B45" r:id="rId43" xr:uid="{00000000-0004-0000-1300-00002A000000}"/>
+    <hyperlink ref="B46" r:id="rId44" xr:uid="{00000000-0004-0000-1300-00002B000000}"/>
+    <hyperlink ref="B48" r:id="rId45" xr:uid="{00000000-0004-0000-1300-00002C000000}"/>
+    <hyperlink ref="B49" r:id="rId46" xr:uid="{00000000-0004-0000-1300-00002D000000}"/>
+    <hyperlink ref="B50" r:id="rId47" xr:uid="{00000000-0004-0000-1300-00002E000000}"/>
+    <hyperlink ref="B51" r:id="rId48" xr:uid="{00000000-0004-0000-1300-00002F000000}"/>
+    <hyperlink ref="B52" r:id="rId49" xr:uid="{00000000-0004-0000-1300-000030000000}"/>
+    <hyperlink ref="B53" r:id="rId50" xr:uid="{00000000-0004-0000-1300-000031000000}"/>
+    <hyperlink ref="B54" r:id="rId51" xr:uid="{00000000-0004-0000-1300-000032000000}"/>
+    <hyperlink ref="B55" r:id="rId52" xr:uid="{00000000-0004-0000-1300-000033000000}"/>
+    <hyperlink ref="B56" r:id="rId53" xr:uid="{00000000-0004-0000-1300-000034000000}"/>
+    <hyperlink ref="B57" r:id="rId54" xr:uid="{00000000-0004-0000-1300-000035000000}"/>
+    <hyperlink ref="B58" r:id="rId55" xr:uid="{00000000-0004-0000-1300-000036000000}"/>
+    <hyperlink ref="B59" r:id="rId56" xr:uid="{00000000-0004-0000-1300-000037000000}"/>
+    <hyperlink ref="B60" r:id="rId57" xr:uid="{00000000-0004-0000-1300-000038000000}"/>
+    <hyperlink ref="B61" r:id="rId58" xr:uid="{00000000-0004-0000-1300-000039000000}"/>
+    <hyperlink ref="B62" r:id="rId59" xr:uid="{00000000-0004-0000-1300-00003A000000}"/>
+    <hyperlink ref="B63" r:id="rId60" xr:uid="{00000000-0004-0000-1300-00003B000000}"/>
+    <hyperlink ref="B64" r:id="rId61" xr:uid="{00000000-0004-0000-1300-00003C000000}"/>
+    <hyperlink ref="B65" r:id="rId62" xr:uid="{00000000-0004-0000-1300-00003D000000}"/>
+    <hyperlink ref="B66" r:id="rId63" xr:uid="{00000000-0004-0000-1300-00003E000000}"/>
   </hyperlinks>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="1.3775590551181103" bottom="1.3775590551181103" header="0.98385826771653551" footer="0.98385826771653551"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -14768,38 +14759,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+    </row>
+    <row r="2" spans="1:4" ht="35.5" customHeight="1">
+      <c r="A2" s="187" t="s">
         <v>711</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-    </row>
-    <row r="2" spans="1:4" ht="35.5" customHeight="1">
-      <c r="A2" s="186" t="s">
-        <v>712</v>
-      </c>
-      <c r="B2" s="186"/>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
+      <c r="B2" s="187"/>
+      <c r="C2" s="187"/>
+      <c r="D2" s="187"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="65" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="67"/>
@@ -14807,7 +14798,7 @@
     </row>
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="65" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="67"/>
@@ -14815,7 +14806,7 @@
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="65" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="67"/>
@@ -14823,7 +14814,7 @@
     </row>
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="65" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="67"/>
@@ -14831,7 +14822,7 @@
     </row>
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="65" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B8" s="66"/>
       <c r="C8" s="67"/>
@@ -14839,7 +14830,7 @@
     </row>
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="65" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="67"/>
@@ -14847,7 +14838,7 @@
     </row>
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="65" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="68"/>
@@ -14855,7 +14846,7 @@
     </row>
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="65" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="68"/>
@@ -14863,7 +14854,7 @@
     </row>
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="65" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B12" s="66"/>
       <c r="C12" s="68"/>
@@ -14871,7 +14862,7 @@
     </row>
     <row r="13" spans="1:4" ht="22">
       <c r="A13" s="65" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="68"/>
@@ -14879,7 +14870,7 @@
     </row>
     <row r="14" spans="1:4" ht="22">
       <c r="A14" s="65" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B14" s="67"/>
       <c r="C14" s="68"/>
@@ -14887,7 +14878,7 @@
     </row>
     <row r="15" spans="1:4" ht="22">
       <c r="A15" s="65" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B15" s="66"/>
       <c r="C15" s="68"/>
@@ -14895,7 +14886,7 @@
     </row>
     <row r="16" spans="1:4" ht="22">
       <c r="A16" s="65" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="68"/>
@@ -14903,7 +14894,7 @@
     </row>
     <row r="17" spans="1:4" ht="22">
       <c r="A17" s="65" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B17" s="67"/>
       <c r="C17" s="68"/>
@@ -14911,7 +14902,7 @@
     </row>
     <row r="18" spans="1:4" ht="22">
       <c r="A18" s="65" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="68"/>
@@ -14919,7 +14910,7 @@
     </row>
     <row r="19" spans="1:4" ht="22">
       <c r="A19" s="65" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="68"/>
@@ -14927,7 +14918,7 @@
     </row>
     <row r="20" spans="1:4" ht="22">
       <c r="A20" s="65" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="68"/>
@@ -14935,7 +14926,7 @@
     </row>
     <row r="21" spans="1:4" ht="22">
       <c r="A21" s="65" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B21" s="66"/>
       <c r="C21" s="68"/>
@@ -14943,7 +14934,7 @@
     </row>
     <row r="22" spans="1:4" ht="22">
       <c r="A22" s="65" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="68"/>
@@ -14994,38 +14985,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="187" t="s">
         <v>736</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="186" t="s">
-        <v>737</v>
-      </c>
-      <c r="B2" s="186"/>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
+      <c r="B2" s="187"/>
+      <c r="C2" s="187"/>
+      <c r="D2" s="187"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="65" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="67"/>
@@ -15033,7 +15024,7 @@
     </row>
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="65" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="67"/>
@@ -15041,7 +15032,7 @@
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="65" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="67"/>
@@ -15049,7 +15040,7 @@
     </row>
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="65" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="67"/>
@@ -15057,7 +15048,7 @@
     </row>
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="65" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B8" s="66"/>
       <c r="C8" s="67"/>
@@ -15065,7 +15056,7 @@
     </row>
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="65" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="67"/>
@@ -15073,7 +15064,7 @@
     </row>
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="65" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="68"/>
@@ -15081,7 +15072,7 @@
     </row>
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="65" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="68"/>
@@ -15089,7 +15080,7 @@
     </row>
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="65" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B12" s="66"/>
       <c r="C12" s="68"/>
@@ -15097,7 +15088,7 @@
     </row>
     <row r="13" spans="1:4" ht="22">
       <c r="A13" s="65" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="68"/>
@@ -15105,7 +15096,7 @@
     </row>
     <row r="14" spans="1:4" ht="22">
       <c r="A14" s="65" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B14" s="67"/>
       <c r="C14" s="68"/>
@@ -15113,7 +15104,7 @@
     </row>
     <row r="15" spans="1:4" ht="22">
       <c r="A15" s="65" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B15" s="66"/>
       <c r="C15" s="68"/>
@@ -15121,7 +15112,7 @@
     </row>
     <row r="16" spans="1:4" ht="22">
       <c r="A16" s="65" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="68"/>
@@ -15129,7 +15120,7 @@
     </row>
     <row r="17" spans="1:4" ht="22">
       <c r="A17" s="65" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B17" s="67"/>
       <c r="C17" s="68"/>
@@ -15137,7 +15128,7 @@
     </row>
     <row r="18" spans="1:4" ht="22">
       <c r="A18" s="65" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="68"/>
@@ -15183,38 +15174,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
+        <v>752</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="187" t="s">
         <v>753</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="186" t="s">
-        <v>754</v>
-      </c>
-      <c r="B2" s="186"/>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
+      <c r="B2" s="187"/>
+      <c r="C2" s="187"/>
+      <c r="D2" s="187"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="67" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -15223,7 +15214,7 @@
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="30"/>
       <c r="B5" s="67" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C5" s="67"/>
       <c r="D5" s="68"/>
@@ -15231,14 +15222,14 @@
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="30"/>
       <c r="B6" s="67" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C6" s="67"/>
       <c r="D6" s="68"/>
     </row>
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="67" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B7" s="67"/>
       <c r="C7" s="67"/>
@@ -15247,7 +15238,7 @@
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="30"/>
       <c r="B8" s="67" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="68"/>
@@ -15255,7 +15246,7 @@
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="30"/>
       <c r="B9" s="67" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="68"/>
@@ -15263,14 +15254,14 @@
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="30"/>
       <c r="B10" s="67" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C10" s="68"/>
       <c r="D10" s="68"/>
     </row>
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="67" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B11" s="67"/>
       <c r="C11" s="68"/>
@@ -15279,7 +15270,7 @@
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="30"/>
       <c r="B12" s="67" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C12" s="68"/>
       <c r="D12" s="68"/>
@@ -15287,7 +15278,7 @@
     <row r="13" spans="1:4" ht="22">
       <c r="A13" s="30"/>
       <c r="B13" s="67" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C13" s="68"/>
       <c r="D13" s="68"/>
@@ -15295,7 +15286,7 @@
     <row r="14" spans="1:4" ht="22">
       <c r="A14" s="30"/>
       <c r="B14" s="67" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C14" s="68"/>
       <c r="D14" s="68"/>
@@ -15303,7 +15294,7 @@
     <row r="15" spans="1:4" ht="22">
       <c r="A15" s="30"/>
       <c r="B15" s="67" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="68"/>
@@ -15311,7 +15302,7 @@
     <row r="16" spans="1:4" ht="22">
       <c r="A16" s="30"/>
       <c r="B16" s="67" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C16" s="68"/>
       <c r="D16" s="68"/>
@@ -15319,7 +15310,7 @@
     <row r="17" spans="1:4" ht="22">
       <c r="A17" s="30"/>
       <c r="B17" s="67" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C17" s="68"/>
       <c r="D17" s="68"/>
@@ -15327,7 +15318,7 @@
     <row r="18" spans="1:4" ht="22">
       <c r="A18" s="30"/>
       <c r="B18" s="67" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C18" s="68"/>
       <c r="D18" s="68"/>
@@ -15355,38 +15346,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
+        <v>769</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="188" t="s">
         <v>770</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="187" t="s">
-        <v>771</v>
-      </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="67" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -15394,7 +15385,7 @@
     </row>
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="67" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B5" s="67"/>
       <c r="C5" s="67"/>
@@ -15402,7 +15393,7 @@
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="67" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
@@ -15431,33 +15422,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
+        <v>774</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="188" t="s">
         <v>775</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="187" t="s">
-        <v>776</v>
-      </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
@@ -15470,7 +15461,7 @@
     </row>
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="67" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B5" s="67"/>
       <c r="C5" s="67"/>
@@ -15478,7 +15469,7 @@
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="67" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
@@ -15509,38 +15500,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
+        <v>778</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="189" t="s">
         <v>779</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="188" t="s">
-        <v>780</v>
-      </c>
-      <c r="B2" s="188"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
+      <c r="B2" s="189"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="65" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="67"/>
@@ -15549,7 +15540,7 @@
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="66"/>
       <c r="B5" s="65" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C5" s="67"/>
       <c r="D5" s="68"/>
@@ -15557,7 +15548,7 @@
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="66"/>
       <c r="B6" s="65" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C6" s="67"/>
       <c r="D6" s="68"/>
@@ -15565,7 +15556,7 @@
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="66"/>
       <c r="B7" s="65" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="68"/>
@@ -15573,7 +15564,7 @@
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="66"/>
       <c r="B8" s="65" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="68"/>
@@ -15581,14 +15572,14 @@
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="66"/>
       <c r="B9" s="65" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="68"/>
     </row>
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="65" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="68"/>
@@ -15597,7 +15588,7 @@
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="67"/>
       <c r="B11" s="65" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C11" s="68"/>
       <c r="D11" s="68"/>
@@ -15605,7 +15596,7 @@
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="67"/>
       <c r="B12" s="65" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C12" s="68"/>
       <c r="D12" s="68"/>
@@ -15613,14 +15604,14 @@
     <row r="13" spans="1:4" ht="22">
       <c r="A13" s="67"/>
       <c r="B13" s="65" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C13" s="68"/>
       <c r="D13" s="68"/>
     </row>
     <row r="14" spans="1:4" ht="22">
       <c r="A14" s="65" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B14" s="67"/>
       <c r="C14" s="68"/>
@@ -15629,7 +15620,7 @@
     <row r="15" spans="1:4" ht="22">
       <c r="A15" s="67"/>
       <c r="B15" s="65" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="68"/>
@@ -15637,14 +15628,14 @@
     <row r="16" spans="1:4" ht="22">
       <c r="A16" s="67"/>
       <c r="B16" s="65" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C16" s="68"/>
       <c r="D16" s="68"/>
     </row>
     <row r="17" spans="1:4" ht="22">
       <c r="A17" s="65" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B17" s="67"/>
       <c r="C17" s="68"/>
@@ -15653,7 +15644,7 @@
     <row r="18" spans="1:4" ht="22">
       <c r="A18" s="67"/>
       <c r="B18" s="65" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C18" s="68"/>
       <c r="D18" s="68"/>
@@ -15661,7 +15652,7 @@
     <row r="19" spans="1:4" ht="22">
       <c r="A19" s="67"/>
       <c r="B19" s="65" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C19" s="68"/>
       <c r="D19" s="68"/>
@@ -15669,7 +15660,7 @@
     <row r="20" spans="1:4" ht="22">
       <c r="A20" s="67"/>
       <c r="B20" s="65" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C20" s="68"/>
       <c r="D20" s="68"/>
@@ -15677,7 +15668,7 @@
     <row r="21" spans="1:4" ht="22">
       <c r="A21" s="67"/>
       <c r="B21" s="65" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C21" s="68"/>
       <c r="D21" s="68"/>
@@ -15685,7 +15676,7 @@
     <row r="22" spans="1:4" ht="22">
       <c r="A22" s="67"/>
       <c r="B22" s="65" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C22" s="68"/>
       <c r="D22" s="68"/>
@@ -15693,7 +15684,7 @@
     <row r="23" spans="1:4" ht="22">
       <c r="A23" s="67"/>
       <c r="B23" s="65" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C23" s="68"/>
       <c r="D23" s="68"/>
@@ -15701,7 +15692,7 @@
     <row r="24" spans="1:4" ht="22">
       <c r="A24" s="67"/>
       <c r="B24" s="65" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C24" s="68"/>
       <c r="D24" s="68"/>
@@ -15709,7 +15700,7 @@
     <row r="25" spans="1:4" ht="22">
       <c r="A25" s="67"/>
       <c r="B25" s="65" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C25" s="68"/>
       <c r="D25" s="68"/>
@@ -15717,7 +15708,7 @@
     <row r="26" spans="1:4" ht="22">
       <c r="A26" s="67"/>
       <c r="B26" s="65" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="68"/>
@@ -15725,7 +15716,7 @@
     <row r="27" spans="1:4" ht="22">
       <c r="A27" s="67"/>
       <c r="B27" s="65" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C27" s="68"/>
       <c r="D27" s="68"/>
@@ -15733,7 +15724,7 @@
     <row r="28" spans="1:4" ht="22">
       <c r="A28" s="67"/>
       <c r="B28" s="65" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C28" s="68"/>
       <c r="D28" s="68"/>
@@ -15741,7 +15732,7 @@
     <row r="29" spans="1:4" ht="22">
       <c r="A29" s="67"/>
       <c r="B29" s="65" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C29" s="68"/>
       <c r="D29" s="68"/>
@@ -15749,7 +15740,7 @@
     <row r="30" spans="1:4" ht="22">
       <c r="A30" s="67"/>
       <c r="B30" s="65" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C30" s="68"/>
       <c r="D30" s="68"/>
@@ -15757,7 +15748,7 @@
     <row r="31" spans="1:4" ht="22">
       <c r="A31" s="67"/>
       <c r="B31" s="65" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C31" s="68"/>
       <c r="D31" s="68"/>
@@ -15765,14 +15756,14 @@
     <row r="32" spans="1:4" ht="22">
       <c r="A32" s="67"/>
       <c r="B32" s="65" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C32" s="68"/>
       <c r="D32" s="68"/>
     </row>
     <row r="33" spans="1:4" ht="22">
       <c r="A33" s="65" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B33" s="67"/>
       <c r="C33" s="68"/>
@@ -15781,7 +15772,7 @@
     <row r="34" spans="1:4" ht="22">
       <c r="A34" s="67"/>
       <c r="B34" s="65" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C34" s="68"/>
       <c r="D34" s="68"/>
@@ -15789,7 +15780,7 @@
     <row r="35" spans="1:4" ht="22">
       <c r="A35" s="67"/>
       <c r="B35" s="65" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C35" s="68"/>
       <c r="D35" s="68"/>
@@ -15797,7 +15788,7 @@
     <row r="36" spans="1:4" ht="22">
       <c r="A36" s="67"/>
       <c r="B36" s="65" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C36" s="68"/>
       <c r="D36" s="68"/>
@@ -15805,7 +15796,7 @@
     <row r="37" spans="1:4" ht="22">
       <c r="A37" s="67"/>
       <c r="B37" s="65" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C37" s="68"/>
       <c r="D37" s="68"/>
@@ -15813,7 +15804,7 @@
     <row r="38" spans="1:4" ht="22">
       <c r="A38" s="66"/>
       <c r="B38" s="69" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C38" s="68"/>
       <c r="D38" s="68"/>
@@ -15821,7 +15812,7 @@
     <row r="39" spans="1:4" ht="22">
       <c r="A39" s="66"/>
       <c r="B39" s="69" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C39" s="68"/>
       <c r="D39" s="68"/>
@@ -15829,7 +15820,7 @@
     <row r="40" spans="1:4" ht="22">
       <c r="A40" s="66"/>
       <c r="B40" s="69" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C40" s="68"/>
       <c r="D40" s="68"/>
@@ -15837,7 +15828,7 @@
     <row r="41" spans="1:4" ht="22">
       <c r="A41" s="66"/>
       <c r="B41" s="69" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C41" s="68"/>
       <c r="D41" s="68"/>
@@ -15845,7 +15836,7 @@
     <row r="42" spans="1:4" ht="22">
       <c r="A42" s="66"/>
       <c r="B42" s="69" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C42" s="68"/>
       <c r="D42" s="68"/>
@@ -15853,7 +15844,7 @@
     <row r="43" spans="1:4" ht="22">
       <c r="A43" s="66"/>
       <c r="B43" s="69" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C43" s="68"/>
       <c r="D43" s="68"/>
@@ -15861,7 +15852,7 @@
     <row r="44" spans="1:4" ht="22">
       <c r="A44" s="66"/>
       <c r="B44" s="69" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C44" s="68"/>
       <c r="D44" s="68"/>
@@ -15869,7 +15860,7 @@
     <row r="45" spans="1:4" ht="22">
       <c r="A45" s="66"/>
       <c r="B45" s="69" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C45" s="68"/>
       <c r="D45" s="68"/>
@@ -15877,7 +15868,7 @@
     <row r="46" spans="1:4" ht="22">
       <c r="A46" s="66"/>
       <c r="B46" s="69" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C46" s="68"/>
       <c r="D46" s="68"/>
@@ -15885,7 +15876,7 @@
     <row r="47" spans="1:4" ht="22">
       <c r="A47" s="66"/>
       <c r="B47" s="69" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C47" s="68"/>
       <c r="D47" s="68"/>
@@ -15893,7 +15884,7 @@
     <row r="48" spans="1:4" ht="22">
       <c r="A48" s="66"/>
       <c r="B48" s="69" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C48" s="68"/>
       <c r="D48" s="68"/>
@@ -15901,7 +15892,7 @@
     <row r="49" spans="1:4" ht="22">
       <c r="A49" s="66"/>
       <c r="B49" s="69" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C49" s="68"/>
       <c r="D49" s="68"/>
@@ -15909,7 +15900,7 @@
     <row r="50" spans="1:4" ht="22">
       <c r="A50" s="66"/>
       <c r="B50" s="69" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C50" s="68"/>
       <c r="D50" s="68"/>
@@ -15917,7 +15908,7 @@
     <row r="51" spans="1:4" ht="22">
       <c r="A51" s="66"/>
       <c r="B51" s="69" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C51" s="68"/>
       <c r="D51" s="68"/>
@@ -15925,14 +15916,14 @@
     <row r="52" spans="1:4" ht="22">
       <c r="A52" s="66"/>
       <c r="B52" s="69" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C52" s="68"/>
       <c r="D52" s="68"/>
     </row>
     <row r="53" spans="1:4" ht="22">
       <c r="A53" s="65" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B53" s="67"/>
       <c r="C53" s="68"/>
@@ -15941,7 +15932,7 @@
     <row r="54" spans="1:4" ht="22">
       <c r="A54" s="67"/>
       <c r="B54" s="65" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C54" s="68"/>
       <c r="D54" s="68"/>
@@ -15949,7 +15940,7 @@
     <row r="55" spans="1:4" ht="22">
       <c r="A55" s="67"/>
       <c r="B55" s="65" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C55" s="68"/>
       <c r="D55" s="68"/>
@@ -15957,7 +15948,7 @@
     <row r="56" spans="1:4" ht="22">
       <c r="A56" s="67"/>
       <c r="B56" s="65" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C56" s="68"/>
       <c r="D56" s="68"/>
@@ -15965,7 +15956,7 @@
     <row r="57" spans="1:4" ht="22">
       <c r="A57" s="67"/>
       <c r="B57" s="65" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C57" s="68"/>
       <c r="D57" s="68"/>
@@ -15973,14 +15964,14 @@
     <row r="58" spans="1:4" ht="22">
       <c r="A58" s="67"/>
       <c r="B58" s="65" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C58" s="68"/>
       <c r="D58" s="68"/>
     </row>
     <row r="59" spans="1:4" ht="22">
       <c r="A59" s="65" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B59" s="67"/>
       <c r="C59" s="68"/>
@@ -15989,7 +15980,7 @@
     <row r="60" spans="1:4" ht="22">
       <c r="A60" s="67"/>
       <c r="B60" s="65" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C60" s="68"/>
       <c r="D60" s="68"/>
@@ -15997,7 +15988,7 @@
     <row r="61" spans="1:4" ht="22">
       <c r="A61" s="67"/>
       <c r="B61" s="65" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C61" s="68"/>
       <c r="D61" s="68"/>
@@ -16005,7 +15996,7 @@
     <row r="62" spans="1:4" ht="22">
       <c r="A62" s="67"/>
       <c r="B62" s="65" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C62" s="68"/>
       <c r="D62" s="68"/>
@@ -16013,14 +16004,14 @@
     <row r="63" spans="1:4" ht="22">
       <c r="A63" s="67"/>
       <c r="B63" s="65" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C63" s="68"/>
       <c r="D63" s="68"/>
     </row>
     <row r="64" spans="1:4" ht="22">
       <c r="A64" s="65" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B64" s="67"/>
       <c r="C64" s="68"/>
@@ -16029,7 +16020,7 @@
     <row r="65" spans="1:4" ht="22">
       <c r="A65" s="67"/>
       <c r="B65" s="65" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C65" s="68"/>
       <c r="D65" s="68"/>
@@ -16037,7 +16028,7 @@
     <row r="66" spans="1:4" ht="22">
       <c r="A66" s="67"/>
       <c r="B66" s="65" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C66" s="68"/>
       <c r="D66" s="68"/>
@@ -16045,7 +16036,7 @@
     <row r="67" spans="1:4" ht="22">
       <c r="A67" s="67"/>
       <c r="B67" s="65" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C67" s="68"/>
       <c r="D67" s="68"/>
@@ -16053,7 +16044,7 @@
     <row r="68" spans="1:4" ht="22">
       <c r="A68" s="67"/>
       <c r="B68" s="65" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C68" s="68"/>
       <c r="D68" s="68"/>
@@ -16061,7 +16052,7 @@
     <row r="69" spans="1:4" ht="22">
       <c r="A69" s="67"/>
       <c r="B69" s="65" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C69" s="68"/>
       <c r="D69" s="68"/>
@@ -16069,7 +16060,7 @@
     <row r="70" spans="1:4" ht="22">
       <c r="A70" s="67"/>
       <c r="B70" s="65" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C70" s="68"/>
       <c r="D70" s="68"/>
@@ -16077,7 +16068,7 @@
     <row r="71" spans="1:4" ht="22">
       <c r="A71" s="67"/>
       <c r="B71" s="65" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C71" s="68"/>
       <c r="D71" s="68"/>
@@ -16085,14 +16076,14 @@
     <row r="72" spans="1:4" ht="22">
       <c r="A72" s="67"/>
       <c r="B72" s="65" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C72" s="68"/>
       <c r="D72" s="68"/>
     </row>
     <row r="73" spans="1:4" ht="22">
       <c r="A73" s="65" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B73" s="67"/>
       <c r="C73" s="68"/>
@@ -16101,7 +16092,7 @@
     <row r="74" spans="1:4" ht="22">
       <c r="A74" s="67"/>
       <c r="B74" s="65" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C74" s="68"/>
       <c r="D74" s="68"/>
@@ -16109,7 +16100,7 @@
     <row r="75" spans="1:4" ht="22">
       <c r="A75" s="67"/>
       <c r="B75" s="65" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C75" s="68"/>
       <c r="D75" s="68"/>
@@ -16117,7 +16108,7 @@
     <row r="76" spans="1:4" ht="22">
       <c r="A76" s="67"/>
       <c r="B76" s="65" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C76" s="68"/>
       <c r="D76" s="68"/>
@@ -16125,7 +16116,7 @@
     <row r="77" spans="1:4" ht="22">
       <c r="A77" s="67"/>
       <c r="B77" s="65" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C77" s="68"/>
       <c r="D77" s="68"/>
@@ -16133,7 +16124,7 @@
     <row r="78" spans="1:4" ht="22">
       <c r="A78" s="67"/>
       <c r="B78" s="65" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C78" s="68"/>
       <c r="D78" s="68"/>
@@ -16141,7 +16132,7 @@
     <row r="79" spans="1:4" ht="22">
       <c r="A79" s="67"/>
       <c r="B79" s="65" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C79" s="68"/>
       <c r="D79" s="68"/>
@@ -16149,14 +16140,14 @@
     <row r="80" spans="1:4" ht="22">
       <c r="A80" s="67"/>
       <c r="B80" s="65" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C80" s="68"/>
       <c r="D80" s="68"/>
     </row>
     <row r="81" spans="1:4" ht="22">
       <c r="A81" s="65" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B81" s="67"/>
       <c r="C81" s="68"/>
@@ -16165,7 +16156,7 @@
     <row r="82" spans="1:4" ht="22">
       <c r="A82" s="67"/>
       <c r="B82" s="65" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C82" s="68"/>
       <c r="D82" s="68"/>
@@ -16173,14 +16164,14 @@
     <row r="83" spans="1:4" ht="22">
       <c r="A83" s="67"/>
       <c r="B83" s="65" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C83" s="68"/>
       <c r="D83" s="68"/>
     </row>
     <row r="84" spans="1:4" ht="22">
       <c r="A84" s="65" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B84" s="67"/>
       <c r="C84" s="67"/>
@@ -16189,7 +16180,7 @@
     <row r="85" spans="1:4" ht="22">
       <c r="A85" s="67"/>
       <c r="B85" s="65" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C85" s="67"/>
       <c r="D85" s="70"/>
@@ -16197,7 +16188,7 @@
     <row r="86" spans="1:4" ht="22">
       <c r="A86" s="67"/>
       <c r="B86" s="65" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C86" s="67"/>
       <c r="D86" s="70"/>
@@ -16205,14 +16196,14 @@
     <row r="87" spans="1:4" ht="22">
       <c r="A87" s="67"/>
       <c r="B87" s="65" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C87" s="67"/>
       <c r="D87" s="70"/>
     </row>
     <row r="88" spans="1:4" ht="22">
       <c r="A88" s="65" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B88" s="67"/>
       <c r="C88" s="67"/>
@@ -16221,7 +16212,7 @@
     <row r="89" spans="1:4" ht="22">
       <c r="A89" s="67"/>
       <c r="B89" s="65" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C89" s="67"/>
       <c r="D89" s="70"/>
@@ -16229,7 +16220,7 @@
     <row r="90" spans="1:4" ht="22">
       <c r="A90" s="67"/>
       <c r="B90" s="65" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C90" s="67"/>
       <c r="D90" s="70"/>
@@ -16237,7 +16228,7 @@
     <row r="91" spans="1:4" ht="22">
       <c r="A91" s="67"/>
       <c r="B91" s="65" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C91" s="67"/>
       <c r="D91" s="70"/>
@@ -16245,14 +16236,14 @@
     <row r="92" spans="1:4" ht="22">
       <c r="A92" s="67"/>
       <c r="B92" s="65" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C92" s="67"/>
       <c r="D92" s="70"/>
     </row>
     <row r="93" spans="1:4" ht="22">
       <c r="A93" s="65" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B93" s="67"/>
       <c r="C93" s="67"/>
@@ -16261,7 +16252,7 @@
     <row r="94" spans="1:4" ht="22">
       <c r="A94" s="67"/>
       <c r="B94" s="65" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C94" s="67"/>
       <c r="D94" s="70"/>
@@ -16269,7 +16260,7 @@
     <row r="95" spans="1:4" ht="22">
       <c r="A95" s="67"/>
       <c r="B95" s="65" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C95" s="67"/>
       <c r="D95" s="70"/>
@@ -16277,7 +16268,7 @@
     <row r="96" spans="1:4" ht="22">
       <c r="A96" s="67"/>
       <c r="B96" s="65" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C96" s="67"/>
       <c r="D96" s="70"/>
@@ -16285,7 +16276,7 @@
     <row r="97" spans="1:4" ht="22">
       <c r="A97" s="67"/>
       <c r="B97" s="65" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C97" s="67"/>
       <c r="D97" s="70"/>
@@ -16413,38 +16404,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="190" t="s">
+        <v>874</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="186" t="s">
         <v>875</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="185" t="s">
-        <v>876</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="65" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B4" s="68"/>
       <c r="C4" s="68"/>
@@ -16453,7 +16444,7 @@
     <row r="5" spans="1:4" ht="23">
       <c r="A5" s="67"/>
       <c r="B5" s="71" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C5" s="68"/>
       <c r="D5" s="68"/>
@@ -16462,7 +16453,7 @@
       <c r="A6" s="67"/>
       <c r="B6" s="68"/>
       <c r="C6" s="71" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D6" s="68"/>
     </row>
@@ -16470,7 +16461,7 @@
       <c r="A7" s="67"/>
       <c r="B7" s="68"/>
       <c r="C7" s="71" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D7" s="68"/>
     </row>
@@ -16478,7 +16469,7 @@
       <c r="A8" s="67"/>
       <c r="B8" s="68"/>
       <c r="C8" s="71" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D8" s="68"/>
     </row>
@@ -16486,7 +16477,7 @@
       <c r="A9" s="67"/>
       <c r="B9" s="68"/>
       <c r="C9" s="71" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D9" s="68"/>
     </row>
@@ -16494,7 +16485,7 @@
       <c r="A10" s="67"/>
       <c r="B10" s="68"/>
       <c r="C10" s="71" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D10" s="68"/>
     </row>
@@ -16502,7 +16493,7 @@
       <c r="A11" s="67"/>
       <c r="B11" s="68"/>
       <c r="C11" s="71" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D11" s="68"/>
     </row>
@@ -16510,7 +16501,7 @@
       <c r="A12" s="67"/>
       <c r="B12" s="68"/>
       <c r="C12" s="71" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D12" s="68"/>
     </row>
@@ -16518,7 +16509,7 @@
       <c r="A13" s="67"/>
       <c r="B13" s="68"/>
       <c r="C13" s="71" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D13" s="68"/>
     </row>
@@ -16526,14 +16517,14 @@
       <c r="A14" s="67"/>
       <c r="B14" s="68"/>
       <c r="C14" s="71" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D14" s="68"/>
     </row>
     <row r="15" spans="1:4" ht="23">
       <c r="A15" s="67"/>
       <c r="B15" s="71" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="68"/>
@@ -16542,7 +16533,7 @@
       <c r="A16" s="67"/>
       <c r="B16" s="68"/>
       <c r="C16" s="71" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D16" s="68"/>
     </row>
@@ -16550,7 +16541,7 @@
       <c r="A17" s="67"/>
       <c r="B17" s="68"/>
       <c r="C17" s="71" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D17" s="68"/>
     </row>
@@ -16558,7 +16549,7 @@
       <c r="A18" s="67"/>
       <c r="B18" s="68"/>
       <c r="C18" s="71" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D18" s="68"/>
     </row>
@@ -16566,7 +16557,7 @@
       <c r="A19" s="67"/>
       <c r="B19" s="68"/>
       <c r="C19" s="71" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D19" s="68"/>
     </row>
@@ -16574,7 +16565,7 @@
       <c r="A20" s="67"/>
       <c r="B20" s="68"/>
       <c r="C20" s="71" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D20" s="68"/>
     </row>
@@ -16582,14 +16573,14 @@
       <c r="A21" s="67"/>
       <c r="B21" s="68"/>
       <c r="C21" s="71" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D21" s="68"/>
     </row>
     <row r="22" spans="1:4" ht="23">
       <c r="A22" s="67"/>
       <c r="B22" s="71" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C22" s="68"/>
       <c r="D22" s="68"/>
@@ -16598,7 +16589,7 @@
       <c r="A23" s="67"/>
       <c r="B23" s="68"/>
       <c r="C23" s="71" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D23" s="68"/>
     </row>
@@ -16606,7 +16597,7 @@
       <c r="A24" s="67"/>
       <c r="B24" s="68"/>
       <c r="C24" s="71" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D24" s="68"/>
     </row>
@@ -16614,14 +16605,14 @@
       <c r="A25" s="67"/>
       <c r="B25" s="68"/>
       <c r="C25" s="71" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D25" s="68"/>
     </row>
     <row r="26" spans="1:4" ht="23">
       <c r="A26" s="67"/>
       <c r="B26" s="71" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C26" s="68"/>
       <c r="D26" s="68"/>
@@ -16630,13 +16621,13 @@
       <c r="A27" s="67"/>
       <c r="B27" s="68"/>
       <c r="C27" s="71" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D27" s="68"/>
     </row>
     <row r="28" spans="1:4" ht="22">
       <c r="A28" s="65" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B28" s="68"/>
       <c r="C28" s="68"/>
@@ -16645,7 +16636,7 @@
     <row r="29" spans="1:4" ht="23">
       <c r="A29" s="67"/>
       <c r="B29" s="71" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C29" s="68"/>
       <c r="D29" s="68"/>
@@ -16654,7 +16645,7 @@
       <c r="A30" s="67"/>
       <c r="B30" s="16"/>
       <c r="C30" s="71" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D30" s="68"/>
     </row>
@@ -16662,14 +16653,14 @@
       <c r="A31" s="67"/>
       <c r="B31" s="16"/>
       <c r="C31" s="71" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D31" s="68"/>
     </row>
     <row r="32" spans="1:4" ht="23">
       <c r="A32" s="67"/>
       <c r="B32" s="71" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C32" s="68"/>
       <c r="D32" s="68"/>
@@ -16678,7 +16669,7 @@
       <c r="A33" s="67"/>
       <c r="B33" s="16"/>
       <c r="C33" s="71" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D33" s="68"/>
     </row>
@@ -16686,14 +16677,14 @@
       <c r="A34" s="67"/>
       <c r="B34" s="16"/>
       <c r="C34" s="71" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D34" s="68"/>
     </row>
     <row r="35" spans="1:4" ht="23">
       <c r="A35" s="67"/>
       <c r="B35" s="71" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C35" s="68"/>
       <c r="D35" s="68"/>
@@ -16702,7 +16693,7 @@
       <c r="A36" s="67"/>
       <c r="B36" s="16"/>
       <c r="C36" s="71" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D36" s="68"/>
     </row>
@@ -16710,14 +16701,14 @@
       <c r="A37" s="67"/>
       <c r="B37" s="16"/>
       <c r="C37" s="71" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D37" s="68"/>
     </row>
     <row r="38" spans="1:4" ht="23">
       <c r="A38" s="67"/>
       <c r="B38" s="71" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C38" s="68"/>
       <c r="D38" s="68"/>
@@ -16726,7 +16717,7 @@
       <c r="A39" s="67"/>
       <c r="B39" s="16"/>
       <c r="C39" s="71" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D39" s="68"/>
     </row>
@@ -16734,7 +16725,7 @@
       <c r="A40" s="67"/>
       <c r="B40" s="16"/>
       <c r="C40" s="71" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D40" s="68"/>
     </row>
@@ -16742,7 +16733,7 @@
       <c r="A41" s="67"/>
       <c r="B41" s="16"/>
       <c r="C41" s="71" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D41" s="68"/>
     </row>
@@ -16750,7 +16741,7 @@
       <c r="A42" s="67"/>
       <c r="B42" s="16"/>
       <c r="C42" s="71" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D42" s="68"/>
     </row>
@@ -16758,7 +16749,7 @@
       <c r="A43" s="67"/>
       <c r="B43" s="16"/>
       <c r="C43" s="71" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D43" s="68"/>
     </row>
@@ -16766,14 +16757,14 @@
       <c r="A44" s="67"/>
       <c r="B44" s="16"/>
       <c r="C44" s="71" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D44" s="68"/>
     </row>
     <row r="45" spans="1:4" ht="23">
       <c r="A45" s="67"/>
       <c r="B45" s="71" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C45" s="68"/>
       <c r="D45" s="68"/>
@@ -16782,7 +16773,7 @@
       <c r="A46" s="67"/>
       <c r="B46" s="16"/>
       <c r="C46" s="71" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D46" s="68"/>
     </row>
@@ -16790,7 +16781,7 @@
       <c r="A47" s="67"/>
       <c r="B47" s="16"/>
       <c r="C47" s="71" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D47" s="68"/>
     </row>
@@ -16798,7 +16789,7 @@
       <c r="A48" s="67"/>
       <c r="B48" s="16"/>
       <c r="C48" s="71" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D48" s="68"/>
     </row>
@@ -16806,17 +16797,17 @@
       <c r="A49" s="67"/>
       <c r="B49" s="16"/>
       <c r="C49" s="71" t="s">
+        <v>921</v>
+      </c>
+      <c r="D49" s="68" t="s">
         <v>922</v>
-      </c>
-      <c r="D49" s="68" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="23">
       <c r="A50" s="67"/>
       <c r="B50" s="16"/>
       <c r="C50" s="71" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D50" s="68"/>
     </row>
@@ -16824,7 +16815,7 @@
       <c r="A51" s="67"/>
       <c r="B51" s="16"/>
       <c r="C51" s="71" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D51" s="68"/>
     </row>
@@ -16832,13 +16823,13 @@
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="71" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D52" s="68"/>
     </row>
     <row r="53" spans="1:4" ht="22">
       <c r="A53" s="65" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="68"/>
@@ -16847,7 +16838,7 @@
     <row r="54" spans="1:4" ht="22">
       <c r="A54" s="67"/>
       <c r="B54" s="72" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C54" s="68"/>
       <c r="D54" s="68"/>
@@ -16856,7 +16847,7 @@
       <c r="A55" s="67"/>
       <c r="B55" s="16"/>
       <c r="C55" s="72" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D55" s="68"/>
     </row>
@@ -16864,7 +16855,7 @@
       <c r="A56" s="67"/>
       <c r="B56" s="16"/>
       <c r="C56" s="72" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D56" s="68"/>
     </row>
@@ -16872,13 +16863,13 @@
       <c r="A57" s="67"/>
       <c r="B57" s="16"/>
       <c r="C57" s="72" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D57" s="68"/>
     </row>
     <row r="58" spans="1:4" ht="22">
       <c r="A58" s="65" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B58" s="68"/>
       <c r="C58" s="68"/>
@@ -16887,7 +16878,7 @@
     <row r="59" spans="1:4" ht="23">
       <c r="A59" s="67"/>
       <c r="B59" s="71" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C59" s="68"/>
       <c r="D59" s="68"/>
@@ -16896,7 +16887,7 @@
       <c r="A60" s="67"/>
       <c r="B60" s="16"/>
       <c r="C60" s="71" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D60" s="68"/>
     </row>
@@ -16904,14 +16895,14 @@
       <c r="A61" s="67"/>
       <c r="B61" s="16"/>
       <c r="C61" s="71" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D61" s="68"/>
     </row>
     <row r="62" spans="1:4" ht="23">
       <c r="A62" s="67"/>
       <c r="B62" s="71" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C62" s="68"/>
       <c r="D62" s="68"/>
@@ -16920,7 +16911,7 @@
       <c r="A63" s="67"/>
       <c r="B63" s="16"/>
       <c r="C63" s="71" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D63" s="68"/>
     </row>
@@ -16928,7 +16919,7 @@
       <c r="A64" s="67"/>
       <c r="B64" s="16"/>
       <c r="C64" s="71" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D64" s="68"/>
     </row>
@@ -16936,14 +16927,14 @@
       <c r="A65" s="67"/>
       <c r="B65" s="16"/>
       <c r="C65" s="71" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D65" s="68"/>
     </row>
     <row r="66" spans="1:4" ht="23">
       <c r="A66" s="67"/>
       <c r="B66" s="71" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C66" s="68"/>
       <c r="D66" s="68"/>
@@ -16952,13 +16943,13 @@
       <c r="A67" s="67"/>
       <c r="B67" s="16"/>
       <c r="C67" s="71" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D67" s="68"/>
     </row>
     <row r="68" spans="1:4" ht="22">
       <c r="A68" s="65" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B68" s="68"/>
       <c r="C68" s="68"/>
@@ -16967,7 +16958,7 @@
     <row r="69" spans="1:4" ht="23">
       <c r="A69" s="67"/>
       <c r="B69" s="71" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C69" s="68"/>
       <c r="D69" s="68"/>
@@ -16976,7 +16967,7 @@
       <c r="A70" s="67"/>
       <c r="B70" s="16"/>
       <c r="C70" s="71" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D70" s="68"/>
     </row>
@@ -16984,7 +16975,7 @@
       <c r="A71" s="67"/>
       <c r="B71" s="16"/>
       <c r="C71" s="71" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D71" s="68"/>
     </row>
@@ -16992,7 +16983,7 @@
       <c r="A72" s="67"/>
       <c r="B72" s="16"/>
       <c r="C72" s="71" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D72" s="68"/>
     </row>
@@ -17000,7 +16991,7 @@
       <c r="A73" s="67"/>
       <c r="B73" s="16"/>
       <c r="C73" s="71" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D73" s="68"/>
     </row>
@@ -17008,7 +16999,7 @@
       <c r="A74" s="67"/>
       <c r="B74" s="16"/>
       <c r="C74" s="71" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D74" s="68"/>
     </row>
@@ -17016,7 +17007,7 @@
       <c r="A75" s="67"/>
       <c r="B75" s="16"/>
       <c r="C75" s="71" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D75" s="68"/>
     </row>
@@ -17120,33 +17111,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="190" t="s">
+        <v>948</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="186" t="s">
         <v>949</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="185" t="s">
-        <v>950</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="60" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="D3" s="60" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="23">
@@ -17155,16 +17146,16 @@
       </c>
       <c r="B4" s="73"/>
       <c r="D4" s="68" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="23">
       <c r="A5" s="71" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B5" s="73"/>
       <c r="D5" s="68" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="23">
@@ -17173,7 +17164,7 @@
       </c>
       <c r="B6" s="73"/>
       <c r="D6" s="68" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="23">
@@ -17182,7 +17173,7 @@
       </c>
       <c r="B7" s="73"/>
       <c r="D7" s="68" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="23">
@@ -17191,7 +17182,7 @@
       </c>
       <c r="B8" s="73"/>
       <c r="D8" s="68" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="23">
@@ -17200,7 +17191,7 @@
       </c>
       <c r="B9" s="73"/>
       <c r="D9" s="68" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="23">
@@ -17209,7 +17200,7 @@
       </c>
       <c r="B10" s="73"/>
       <c r="D10" s="68" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="23">
@@ -17218,16 +17209,16 @@
       </c>
       <c r="B11" s="73"/>
       <c r="D11" s="68" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="23">
       <c r="A12" s="71" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B12" s="73"/>
       <c r="D12" s="68" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="23">
@@ -17236,25 +17227,25 @@
       </c>
       <c r="B13" s="73"/>
       <c r="D13" s="68" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="23">
       <c r="A14" s="71" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B14" s="73"/>
       <c r="D14" s="68" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="23">
       <c r="A15" s="71" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B15" s="73"/>
       <c r="D15" s="68" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="23">
@@ -17263,7 +17254,7 @@
       </c>
       <c r="B16" s="73"/>
       <c r="D16" s="68" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="23">
@@ -17272,7 +17263,7 @@
       </c>
       <c r="B17" s="73"/>
       <c r="D17" s="68" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="23">
@@ -17281,7 +17272,7 @@
       </c>
       <c r="B18" s="73"/>
       <c r="D18" s="68" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
   </sheetData>
@@ -17326,38 +17317,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="190" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="186" t="s">
         <v>970</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="185" t="s">
-        <v>971</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="65" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -17366,7 +17357,7 @@
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="67"/>
       <c r="B5" s="65" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C5" s="67"/>
       <c r="D5" s="74"/>
@@ -17375,7 +17366,7 @@
       <c r="A6" s="67"/>
       <c r="B6" s="67"/>
       <c r="C6" s="65" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D6" s="74"/>
     </row>
@@ -17383,14 +17374,14 @@
       <c r="A7" s="67"/>
       <c r="B7" s="67"/>
       <c r="C7" s="65" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D7" s="74"/>
     </row>
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="67"/>
       <c r="B8" s="65" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="74"/>
@@ -17399,7 +17390,7 @@
       <c r="A9" s="67"/>
       <c r="B9" s="67"/>
       <c r="C9" s="65" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D9" s="74"/>
     </row>
@@ -17407,7 +17398,7 @@
       <c r="A10" s="67"/>
       <c r="B10" s="67"/>
       <c r="C10" s="65" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D10" s="74"/>
     </row>
@@ -17415,7 +17406,7 @@
       <c r="A11" s="67"/>
       <c r="B11" s="67"/>
       <c r="C11" s="65" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D11" s="74"/>
     </row>
@@ -17423,7 +17414,7 @@
       <c r="A12" s="67"/>
       <c r="B12" s="67"/>
       <c r="C12" s="65" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D12" s="74"/>
     </row>
@@ -17431,7 +17422,7 @@
       <c r="A13" s="67"/>
       <c r="B13" s="67"/>
       <c r="C13" s="65" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="D13" s="74"/>
     </row>
@@ -17439,14 +17430,14 @@
       <c r="A14" s="67"/>
       <c r="B14" s="67"/>
       <c r="C14" s="65" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D14" s="74"/>
     </row>
     <row r="15" spans="1:4" ht="22">
       <c r="A15" s="67"/>
       <c r="B15" s="65" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="74"/>
@@ -17455,7 +17446,7 @@
       <c r="A16" s="67"/>
       <c r="B16" s="67"/>
       <c r="C16" s="65" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D16" s="74"/>
     </row>
@@ -17463,14 +17454,14 @@
       <c r="A17" s="67"/>
       <c r="B17" s="67"/>
       <c r="C17" s="65" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D17" s="74"/>
     </row>
     <row r="18" spans="1:4" ht="22">
       <c r="A18" s="67"/>
       <c r="B18" s="65" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C18" s="67"/>
       <c r="D18" s="74"/>
@@ -17479,7 +17470,7 @@
       <c r="A19" s="67"/>
       <c r="B19" s="67"/>
       <c r="C19" s="65" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D19" s="74"/>
     </row>
@@ -17487,13 +17478,13 @@
       <c r="A20" s="67"/>
       <c r="B20" s="67"/>
       <c r="C20" s="65" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D20" s="74"/>
     </row>
     <row r="21" spans="1:4" ht="22">
       <c r="A21" s="65" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B21" s="75"/>
       <c r="C21" s="75"/>
@@ -17502,7 +17493,7 @@
     <row r="22" spans="1:4" ht="22">
       <c r="A22" s="67"/>
       <c r="B22" s="65" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C22" s="67"/>
       <c r="D22" s="74"/>
@@ -17511,13 +17502,13 @@
       <c r="A23" s="67"/>
       <c r="B23" s="67"/>
       <c r="C23" s="65" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D23" s="74"/>
     </row>
     <row r="24" spans="1:4" ht="22">
       <c r="A24" s="65" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B24" s="67"/>
       <c r="C24" s="67"/>
@@ -17526,7 +17517,7 @@
     <row r="25" spans="1:4" ht="22">
       <c r="A25" s="67"/>
       <c r="B25" s="65" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C25" s="75"/>
       <c r="D25" s="74"/>
@@ -17535,14 +17526,14 @@
       <c r="A26" s="67"/>
       <c r="B26" s="67"/>
       <c r="C26" s="65" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D26" s="74"/>
     </row>
     <row r="27" spans="1:4" ht="22">
       <c r="A27" s="67"/>
       <c r="B27" s="65" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C27" s="75"/>
       <c r="D27" s="74"/>
@@ -17551,14 +17542,14 @@
       <c r="A28" s="67"/>
       <c r="B28" s="67"/>
       <c r="C28" s="65" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D28" s="74"/>
     </row>
     <row r="29" spans="1:4" ht="22">
       <c r="A29" s="67"/>
       <c r="B29" s="65" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C29" s="67"/>
       <c r="D29" s="74"/>
@@ -17567,13 +17558,13 @@
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="65" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D30" s="74"/>
     </row>
     <row r="31" spans="1:4" ht="22">
       <c r="A31" s="65" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B31" s="67"/>
       <c r="C31" s="67"/>
@@ -17582,7 +17573,7 @@
     <row r="32" spans="1:4" ht="22">
       <c r="A32" s="67"/>
       <c r="B32" s="65" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C32" s="75"/>
       <c r="D32" s="74"/>
@@ -17591,7 +17582,7 @@
       <c r="A33" s="67"/>
       <c r="B33" s="67"/>
       <c r="C33" s="65" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D33" s="74"/>
     </row>
@@ -17599,14 +17590,14 @@
       <c r="A34" s="67"/>
       <c r="B34" s="67"/>
       <c r="C34" s="65" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D34" s="74"/>
     </row>
     <row r="35" spans="1:4" ht="22">
       <c r="A35" s="67"/>
       <c r="B35" s="65" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C35" s="67"/>
       <c r="D35" s="74"/>
@@ -17615,7 +17606,7 @@
       <c r="A36" s="67"/>
       <c r="B36" s="67"/>
       <c r="C36" s="65" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D36" s="74"/>
     </row>
@@ -17623,7 +17614,7 @@
       <c r="A37" s="67"/>
       <c r="B37" s="67"/>
       <c r="C37" s="65" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D37" s="74"/>
     </row>
@@ -17631,13 +17622,13 @@
       <c r="A38" s="67"/>
       <c r="B38" s="67"/>
       <c r="C38" s="65" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D38" s="74"/>
     </row>
     <row r="39" spans="1:4" ht="22">
       <c r="A39" s="65" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B39" s="75"/>
       <c r="C39" s="75"/>
@@ -17646,7 +17637,7 @@
     <row r="40" spans="1:4" ht="22">
       <c r="A40" s="67"/>
       <c r="B40" s="65" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C40" s="75"/>
       <c r="D40" s="74"/>
@@ -17655,7 +17646,7 @@
       <c r="A41" s="67"/>
       <c r="B41" s="67"/>
       <c r="C41" s="65" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D41" s="74"/>
     </row>
@@ -17761,38 +17752,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="186" t="s">
         <v>1004</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="185" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="72" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
@@ -17808,7 +17799,7 @@
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="72" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B6" s="46"/>
       <c r="C6" s="46"/>
@@ -17816,7 +17807,7 @@
     </row>
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="72" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B7" s="46"/>
       <c r="C7" s="46"/>
@@ -17824,7 +17815,7 @@
     </row>
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="72" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B8" s="46"/>
       <c r="C8" s="46"/>
@@ -17832,7 +17823,7 @@
     </row>
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="72" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B9" s="46"/>
       <c r="C9" s="46"/>
@@ -17840,7 +17831,7 @@
     </row>
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="72" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B10" s="46"/>
       <c r="C10" s="46"/>
@@ -17848,7 +17839,7 @@
     </row>
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="72" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B11" s="46"/>
       <c r="C11" s="46"/>
@@ -17856,7 +17847,7 @@
     </row>
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="72" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B12" s="46"/>
       <c r="C12" s="46"/>
@@ -17906,38 +17897,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+    </row>
+    <row r="2" spans="1:4" ht="49" customHeight="1">
+      <c r="A2" s="186" t="s">
         <v>1014</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-    </row>
-    <row r="2" spans="1:4" ht="49" customHeight="1">
-      <c r="A2" s="185" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="67" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -17945,7 +17936,7 @@
     </row>
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="67" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B5" s="67"/>
       <c r="C5" s="67"/>
@@ -17953,7 +17944,7 @@
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="67" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
@@ -17961,7 +17952,7 @@
     </row>
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="67" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B7" s="67"/>
       <c r="C7" s="67"/>
@@ -17969,7 +17960,7 @@
     </row>
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="67" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B8" s="67"/>
       <c r="C8" s="67"/>
@@ -17978,7 +17969,7 @@
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="67"/>
       <c r="B9" s="67" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="68"/>
@@ -17986,7 +17977,7 @@
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="67"/>
       <c r="B10" s="67" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="68"/>
@@ -17994,7 +17985,7 @@
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="67"/>
       <c r="B11" s="67" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C11" s="67"/>
       <c r="D11" s="68"/>
@@ -18002,7 +17993,7 @@
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="67"/>
       <c r="B12" s="67" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C12" s="67"/>
       <c r="D12" s="68"/>
@@ -18010,7 +18001,7 @@
     <row r="13" spans="1:4" ht="22">
       <c r="A13" s="67"/>
       <c r="B13" s="67" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C13" s="67"/>
       <c r="D13" s="68"/>
@@ -18041,38 +18032,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="190" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="186" t="s">
         <v>1026</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="185" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="66" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -18080,7 +18071,7 @@
     </row>
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="66" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B5" s="67"/>
       <c r="C5" s="67"/>
@@ -18088,7 +18079,7 @@
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="66" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
@@ -18096,7 +18087,7 @@
     </row>
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="66" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="67"/>
       <c r="C7" s="67"/>
@@ -18104,7 +18095,7 @@
     </row>
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="66" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B8" s="67"/>
       <c r="C8" s="67"/>
@@ -18112,7 +18103,7 @@
     </row>
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="66" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B9" s="67"/>
       <c r="C9" s="67"/>
@@ -18120,7 +18111,7 @@
     </row>
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="66" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="67"/>
@@ -18128,7 +18119,7 @@
     </row>
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="66" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B11" s="67"/>
       <c r="C11" s="67"/>
@@ -18136,7 +18127,7 @@
     </row>
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="66" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B12" s="67"/>
       <c r="C12" s="67"/>
@@ -18144,7 +18135,7 @@
     </row>
     <row r="13" spans="1:4" ht="22">
       <c r="A13" s="66" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B13" s="67"/>
       <c r="C13" s="67"/>
@@ -18152,7 +18143,7 @@
     </row>
     <row r="14" spans="1:4" ht="22">
       <c r="A14" s="66" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B14" s="67"/>
       <c r="C14" s="67"/>
@@ -18160,7 +18151,7 @@
     </row>
     <row r="15" spans="1:4" ht="22">
       <c r="A15" s="66" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B15" s="67"/>
       <c r="C15" s="67"/>
@@ -18168,7 +18159,7 @@
     </row>
     <row r="16" spans="1:4" ht="22">
       <c r="A16" s="66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B16" s="67"/>
       <c r="C16" s="67"/>
@@ -18215,38 +18206,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="190" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="186" t="s">
         <v>1040</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="185" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="65" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -18255,7 +18246,7 @@
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="66"/>
       <c r="B5" s="65" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C5" s="67"/>
       <c r="D5" s="74"/>
@@ -18263,7 +18254,7 @@
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="66"/>
       <c r="B6" s="65" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C6" s="67"/>
       <c r="D6" s="74"/>
@@ -18271,7 +18262,7 @@
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="66"/>
       <c r="B7" s="65" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="74"/>
@@ -18279,14 +18270,14 @@
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="66"/>
       <c r="B8" s="65" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="74"/>
     </row>
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="65" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B9" s="67"/>
       <c r="C9" s="67"/>
@@ -18295,7 +18286,7 @@
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="66"/>
       <c r="B10" s="65" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="74"/>
@@ -18303,14 +18294,14 @@
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="66"/>
       <c r="B11" s="65" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C11" s="67"/>
       <c r="D11" s="74"/>
     </row>
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="65" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B12" s="67"/>
       <c r="C12" s="67"/>
@@ -18357,38 +18348,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="190" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="186" t="s">
         <v>1051</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="185" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="67" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -18396,7 +18387,7 @@
     </row>
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="67" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B5" s="67"/>
       <c r="C5" s="67"/>
@@ -18404,7 +18395,7 @@
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="67" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
@@ -18412,7 +18403,7 @@
     </row>
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="67" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B7" s="67"/>
       <c r="C7" s="67"/>
@@ -18420,7 +18411,7 @@
     </row>
     <row r="8" spans="1:4" ht="22">
       <c r="A8" s="67" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B8" s="67"/>
       <c r="C8" s="67"/>
@@ -18428,7 +18419,7 @@
     </row>
     <row r="9" spans="1:4" ht="22">
       <c r="A9" s="67" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B9" s="67"/>
       <c r="C9" s="67"/>
@@ -18436,7 +18427,7 @@
     </row>
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="67" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="67"/>
@@ -18444,7 +18435,7 @@
     </row>
     <row r="11" spans="1:4" ht="22">
       <c r="A11" s="67" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B11" s="67"/>
       <c r="C11" s="67"/>
@@ -18452,7 +18443,7 @@
     </row>
     <row r="12" spans="1:4" ht="22">
       <c r="A12" s="67" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B12" s="67"/>
       <c r="C12" s="67"/>
@@ -18460,7 +18451,7 @@
     </row>
     <row r="13" spans="1:4" ht="22">
       <c r="A13" s="67" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B13" s="67"/>
       <c r="C13" s="67"/>
@@ -18468,7 +18459,7 @@
     </row>
     <row r="14" spans="1:4" ht="22">
       <c r="A14" s="67" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B14" s="67"/>
       <c r="C14" s="67"/>
@@ -18476,7 +18467,7 @@
     </row>
     <row r="15" spans="1:4" ht="22">
       <c r="A15" s="67" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B15" s="67"/>
       <c r="C15" s="67"/>
@@ -18484,7 +18475,7 @@
     </row>
     <row r="16" spans="1:4" ht="22">
       <c r="A16" s="67" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B16" s="67"/>
       <c r="C16" s="67"/>
@@ -18492,7 +18483,7 @@
     </row>
     <row r="17" spans="1:4" ht="22">
       <c r="A17" s="67" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B17" s="67"/>
       <c r="C17" s="67"/>
@@ -18500,7 +18491,7 @@
     </row>
     <row r="18" spans="1:4" ht="22">
       <c r="A18" s="67" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B18" s="67"/>
       <c r="C18" s="67"/>
@@ -18508,7 +18499,7 @@
     </row>
     <row r="19" spans="1:4" ht="22">
       <c r="A19" s="67" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B19" s="67"/>
       <c r="C19" s="67"/>
@@ -18516,7 +18507,7 @@
     </row>
     <row r="20" spans="1:4" ht="22">
       <c r="A20" s="67" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B20" s="67"/>
       <c r="C20" s="67"/>
@@ -18524,7 +18515,7 @@
     </row>
     <row r="21" spans="1:4" ht="22">
       <c r="A21" s="67" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B21" s="67"/>
       <c r="C21" s="67"/>
@@ -18532,7 +18523,7 @@
     </row>
     <row r="22" spans="1:4" ht="22">
       <c r="A22" s="67" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B22" s="67"/>
       <c r="C22" s="67"/>
@@ -18540,7 +18531,7 @@
     </row>
     <row r="23" spans="1:4" ht="22">
       <c r="A23" s="67" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B23" s="67"/>
       <c r="C23" s="67"/>
@@ -18548,7 +18539,7 @@
     </row>
     <row r="24" spans="1:4" ht="22">
       <c r="A24" s="67" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B24" s="67"/>
       <c r="C24" s="67"/>
@@ -18556,7 +18547,7 @@
     </row>
     <row r="25" spans="1:4" ht="22">
       <c r="A25" s="67" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B25" s="67"/>
       <c r="C25" s="67"/>
@@ -18564,7 +18555,7 @@
     </row>
     <row r="26" spans="1:4" ht="22">
       <c r="A26" s="67" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B26" s="67"/>
       <c r="C26" s="67"/>
@@ -18572,7 +18563,7 @@
     </row>
     <row r="27" spans="1:4" ht="22">
       <c r="A27" s="67" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B27" s="67"/>
       <c r="C27" s="67"/>
@@ -18580,7 +18571,7 @@
     </row>
     <row r="28" spans="1:4" ht="22">
       <c r="A28" s="67" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B28" s="67"/>
       <c r="C28" s="67"/>
@@ -18588,7 +18579,7 @@
     </row>
     <row r="29" spans="1:4" ht="22">
       <c r="A29" s="67" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B29" s="67"/>
       <c r="C29" s="67"/>
@@ -18596,7 +18587,7 @@
     </row>
     <row r="30" spans="1:4" ht="22">
       <c r="A30" s="67" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B30" s="67"/>
       <c r="C30" s="67"/>
@@ -18604,7 +18595,7 @@
     </row>
     <row r="31" spans="1:4" ht="22">
       <c r="A31" s="67" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B31" s="67"/>
       <c r="C31" s="67"/>
@@ -18612,7 +18603,7 @@
     </row>
     <row r="32" spans="1:4" ht="22">
       <c r="A32" s="67" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B32" s="67"/>
       <c r="C32" s="67"/>
@@ -18620,7 +18611,7 @@
     </row>
     <row r="33" spans="1:4" ht="22">
       <c r="A33" s="67" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B33" s="67"/>
       <c r="C33" s="67"/>
@@ -18653,38 +18644,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="190" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+    </row>
+    <row r="2" spans="1:4" ht="22">
+      <c r="A2" s="188" t="s">
         <v>1083</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-    </row>
-    <row r="2" spans="1:4" ht="22">
-      <c r="A2" s="187" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
     </row>
     <row r="3" spans="1:4" ht="23">
       <c r="A3" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="C3" s="64" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="D3" s="64" t="s">
         <v>715</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22">
       <c r="A4" s="67" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -18693,14 +18684,14 @@
     <row r="5" spans="1:4" ht="22">
       <c r="A5" s="67"/>
       <c r="B5" s="67" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C5" s="67"/>
       <c r="D5" s="74"/>
     </row>
     <row r="6" spans="1:4" ht="22">
       <c r="A6" s="67" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
@@ -18708,7 +18699,7 @@
     </row>
     <row r="7" spans="1:4" ht="22">
       <c r="A7" s="67" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B7" s="67"/>
       <c r="C7" s="67"/>
@@ -18716,21 +18707,21 @@
     </row>
     <row r="8" spans="1:4" ht="22">
       <c r="B8" s="67" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="74"/>
     </row>
     <row r="9" spans="1:4" ht="22">
       <c r="B9" s="67" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="74"/>
     </row>
     <row r="10" spans="1:4" ht="22">
       <c r="A10" s="67" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="67"/>
@@ -18738,14 +18729,14 @@
     </row>
     <row r="11" spans="1:4" ht="22">
       <c r="B11" s="67" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C11" s="67"/>
       <c r="D11" s="74"/>
     </row>
     <row r="12" spans="1:4" ht="22">
       <c r="B12" s="67" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C12" s="67"/>
       <c r="D12" s="74"/>
@@ -18779,25 +18770,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="23">
       <c r="A1" s="40" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>1094</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="C1" s="40" t="s">
         <v>1095</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="D1" s="40" t="s">
         <v>1096</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="E1" s="40" t="s">
         <v>1097</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="F1" s="40" t="s">
         <v>1098</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="G1" s="40" t="s">
         <v>1099</v>
-      </c>
-      <c r="G1" s="40" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="22">
@@ -18811,10 +18802,10 @@
         <v>219</v>
       </c>
       <c r="D2" s="76" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E2" s="76" t="s">
         <v>1101</v>
-      </c>
-      <c r="E2" s="76" t="s">
-        <v>1102</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>20</v>
@@ -18834,10 +18825,10 @@
         <v>228</v>
       </c>
       <c r="D3" s="76" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E3" s="76" t="s">
         <v>1103</v>
-      </c>
-      <c r="E3" s="76" t="s">
-        <v>1104</v>
       </c>
       <c r="F3" s="18" t="s">
         <v>21</v>
@@ -18855,10 +18846,10 @@
       </c>
       <c r="C4" s="76"/>
       <c r="D4" s="76" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E4" s="76" t="s">
         <v>1105</v>
-      </c>
-      <c r="E4" s="76" t="s">
-        <v>1106</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>22</v>
@@ -18876,10 +18867,10 @@
       </c>
       <c r="C5" s="76"/>
       <c r="D5" s="76" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E5" s="76" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>23</v>
@@ -18895,10 +18886,10 @@
       <c r="B6" s="76"/>
       <c r="C6" s="76"/>
       <c r="D6" s="76" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E6" s="76" t="s">
         <v>1108</v>
-      </c>
-      <c r="E6" s="76" t="s">
-        <v>1109</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>24</v>
@@ -18914,10 +18905,10 @@
       <c r="B7" s="76"/>
       <c r="C7" s="76"/>
       <c r="D7" s="76" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E7" s="76" t="s">
         <v>1110</v>
-      </c>
-      <c r="E7" s="76" t="s">
-        <v>1111</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>25</v>
@@ -18933,10 +18924,10 @@
       <c r="B8" s="76"/>
       <c r="C8" s="76"/>
       <c r="D8" s="76" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E8" s="76" t="s">
         <v>1112</v>
-      </c>
-      <c r="E8" s="76" t="s">
-        <v>1113</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>26</v>
@@ -18952,10 +18943,10 @@
       <c r="B9" s="76"/>
       <c r="C9" s="76"/>
       <c r="D9" s="76" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E9" s="76" t="s">
         <v>1114</v>
-      </c>
-      <c r="E9" s="76" t="s">
-        <v>1115</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>27</v>
@@ -18969,7 +18960,7 @@
       <c r="B10" s="76"/>
       <c r="C10" s="76"/>
       <c r="D10" s="76" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E10" s="76"/>
       <c r="F10" s="18" t="s">
@@ -19107,16 +19098,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23">
       <c r="A1" s="40" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>1117</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="C1" s="40" t="s">
         <v>1118</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="D1" s="40" t="s">
         <v>1119</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18">
@@ -19124,13 +19115,13 @@
         <v>44637</v>
       </c>
       <c r="B2" s="80" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D2" s="80" t="s">
         <v>1121</v>
-      </c>
-      <c r="C2" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D2" s="80" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18">
@@ -19138,13 +19129,13 @@
         <v>44643</v>
       </c>
       <c r="B3" s="80" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D3" s="80" t="s">
         <v>1123</v>
-      </c>
-      <c r="C3" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D3" s="80" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18">
@@ -19152,13 +19143,13 @@
         <v>44677</v>
       </c>
       <c r="B4" s="80" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D4" s="80" t="s">
         <v>1125</v>
-      </c>
-      <c r="C4" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D4" s="80" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="38">
@@ -19166,41 +19157,41 @@
         <v>44719</v>
       </c>
       <c r="B5" s="80" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D5" s="81" t="s">
         <v>1127</v>
-      </c>
-      <c r="C5" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D5" s="81" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="38">
       <c r="A6" s="76" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B6" s="80" t="s">
         <v>1129</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="C6" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D6" s="81" t="s">
         <v>1130</v>
-      </c>
-      <c r="C6" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D6" s="81" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="38">
       <c r="A7" s="76" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B7" s="80" t="s">
         <v>1132</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="C7" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D7" s="81" t="s">
         <v>1133</v>
-      </c>
-      <c r="C7" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D7" s="81" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="38">
@@ -19208,27 +19199,27 @@
         <v>45083</v>
       </c>
       <c r="B8" s="80" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D8" s="81" t="s">
         <v>1135</v>
-      </c>
-      <c r="C8" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D8" s="81" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="38">
       <c r="A9" s="76" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B9" s="80" t="s">
         <v>1137</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="C9" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D9" s="81" t="s">
         <v>1138</v>
-      </c>
-      <c r="C9" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D9" s="81" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="77" customHeight="1">
@@ -19236,13 +19227,13 @@
         <v>45701</v>
       </c>
       <c r="B10" s="80" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C10" s="80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D10" s="80" t="s">
         <v>1171</v>
-      </c>
-      <c r="C10" s="80" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D10" s="80" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18">
@@ -19362,54 +19353,54 @@
       <c r="AA1" s="36"/>
       <c r="AC1" s="39"/>
       <c r="AD1" s="35"/>
-      <c r="AE1" s="172" t="s">
+      <c r="AE1" s="173" t="s">
         <v>90</v>
       </c>
-      <c r="AF1" s="172"/>
-      <c r="AG1" s="172"/>
-      <c r="AH1" s="172"/>
+      <c r="AF1" s="173"/>
+      <c r="AG1" s="173"/>
+      <c r="AH1" s="173"/>
     </row>
     <row r="2" spans="1:34" ht="27">
       <c r="A2" s="40" t="s">
         <v>91</v>
       </c>
       <c r="B2" s="35"/>
-      <c r="C2" s="173" t="s">
+      <c r="C2" s="174" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
       <c r="J2" s="35"/>
-      <c r="K2" s="173" t="s">
+      <c r="K2" s="174" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="174"/>
       <c r="N2" s="35"/>
       <c r="O2" s="39" t="s">
         <v>94</v>
       </c>
       <c r="P2" s="35"/>
-      <c r="Q2" s="173" t="s">
+      <c r="Q2" s="174" t="s">
         <v>95</v>
       </c>
-      <c r="R2" s="173"/>
+      <c r="R2" s="174"/>
       <c r="S2" s="41"/>
       <c r="T2" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="V2" s="173" t="s">
+      <c r="V2" s="174" t="s">
         <v>96</v>
       </c>
-      <c r="W2" s="173"/>
-      <c r="X2" s="173"/>
-      <c r="Y2" s="173"/>
-      <c r="Z2" s="173"/>
-      <c r="AA2" s="173"/>
+      <c r="W2" s="174"/>
+      <c r="X2" s="174"/>
+      <c r="Y2" s="174"/>
+      <c r="Z2" s="174"/>
+      <c r="AA2" s="174"/>
       <c r="AC2" s="39" t="s">
         <v>97</v>
       </c>
@@ -20878,26 +20869,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="104" customFormat="1" ht="38">
-      <c r="A1" s="174" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
+      <c r="A1" s="175" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
     </row>
     <row r="2" spans="1:7" s="104" customFormat="1">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="176" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
     </row>
     <row r="3" spans="1:7" s="104" customFormat="1" ht="23">
       <c r="A3" s="105" t="s">
@@ -20933,7 +20924,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="109" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="109"/>
       <c r="F4" s="109"/>
@@ -21040,26 +21031,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="104" customFormat="1" ht="38">
-      <c r="A1" s="174" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
+      <c r="A1" s="175" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
     </row>
     <row r="2" spans="1:7" s="104" customFormat="1" ht="63.75" customHeight="1">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="176" t="s">
         <v>230</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
     </row>
     <row r="3" spans="1:7" s="104" customFormat="1" ht="23">
       <c r="A3" s="105" t="s">
@@ -21095,7 +21086,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="89" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="89"/>
       <c r="F4" s="89"/>
@@ -21127,13 +21118,13 @@
         <v>234</v>
       </c>
       <c r="B6" s="108" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C6" s="89" t="s">
         <v>219</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E6" s="89"/>
       <c r="F6" s="89"/>
@@ -21450,26 +21441,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="38">
-      <c r="A1" s="176" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
+      <c r="A1" s="177" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
     </row>
     <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="178" t="s">
         <v>265</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
       <c r="A3" s="105" t="s">
@@ -21505,7 +21496,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="127" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -21523,7 +21514,7 @@
         <v>219</v>
       </c>
       <c r="D5" s="127" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E5" s="100"/>
       <c r="F5" s="100"/>
@@ -21562,7 +21553,7 @@
         <v>215</v>
       </c>
       <c r="E7" s="100"/>
-      <c r="F7" s="190" t="s">
+      <c r="F7" s="172" t="s">
         <v>23</v>
       </c>
       <c r="G7" s="100" t="s">
@@ -21853,27 +21844,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="38">
-      <c r="A1" s="176" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
+      <c r="A1" s="177" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
       <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="178" t="s">
         <v>298</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -21911,7 +21902,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="127" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="138"/>
       <c r="F4" s="100"/>
@@ -21994,7 +21985,7 @@
         <v>22</v>
       </c>
       <c r="G8" s="134" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H8" s="139"/>
     </row>
@@ -22180,27 +22171,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="104" customFormat="1" ht="38">
-      <c r="A1" s="176" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
+      <c r="A1" s="177" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
       <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" s="104" customFormat="1">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="179" t="s">
         <v>321</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="178"/>
-      <c r="G2" s="178"/>
+      <c r="B2" s="179"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
       <c r="H2" s="117"/>
     </row>
     <row r="3" spans="1:8" s="104" customFormat="1" ht="23">
@@ -22238,7 +22229,7 @@
         <v>219</v>
       </c>
       <c r="D4" s="108" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E4" s="100"/>
       <c r="F4" s="100"/>
@@ -22256,7 +22247,7 @@
         <v>228</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E5" s="132"/>
       <c r="F5" s="99"/>
@@ -22330,13 +22321,13 @@
         <v>331</v>
       </c>
       <c r="B9" s="108" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C9" s="100" t="s">
         <v>219</v>
       </c>
       <c r="D9" s="108" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E9" s="100"/>
       <c r="F9" s="100"/>
